--- a/Dev_GNC/TableData/CardDataTable.xlsx
+++ b/Dev_GNC/TableData/CardDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProjects\CardGame\CardGameTable\Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBB33BA-AEC7-4CED-9D8E-95C714E98489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C5588D-2DB8-4E6C-90A4-370B8EEAA4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="1" r:id="rId1"/>
@@ -284,22 +284,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>card_assult_skill1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>card_assult_skill2</t>
-  </si>
-  <si>
-    <t>card_assult_skill3</t>
-  </si>
-  <si>
-    <t>card_assult_skill4</t>
-  </si>
-  <si>
-    <t>card_assult_skill5</t>
-  </si>
-  <si>
     <t>card_heavy_skill1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -414,22 +398,6 @@
     <t>text_card_name_scout_skill5</t>
   </si>
   <si>
-    <t>text_card_name_assult_skill1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>text_card_name_assult_skill2</t>
-  </si>
-  <si>
-    <t>text_card_name_assult_skill3</t>
-  </si>
-  <si>
-    <t>text_card_name_assult_skill4</t>
-  </si>
-  <si>
-    <t>text_card_name_assult_skill5</t>
-  </si>
-  <si>
     <t>text_card_name_heavy_skill1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -514,22 +482,6 @@
     <t>text_card_desc_specialist_skill5</t>
   </si>
   <si>
-    <t>text_card_desc_assult_skill1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>text_card_desc_assult_skill2</t>
-  </si>
-  <si>
-    <t>text_card_desc_assult_skill3</t>
-  </si>
-  <si>
-    <t>text_card_desc_assult_skill4</t>
-  </si>
-  <si>
-    <t>text_card_desc_assult_skill5</t>
-  </si>
-  <si>
     <t>text_card_desc_heavy_skill1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -558,6 +510,54 @@
   <si>
     <t>Textures/Card/4</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_assault_skill1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_assault_skill2</t>
+  </si>
+  <si>
+    <t>card_assault_skill3</t>
+  </si>
+  <si>
+    <t>card_assault_skill4</t>
+  </si>
+  <si>
+    <t>card_assault_skill5</t>
+  </si>
+  <si>
+    <t>text_card_name_assault_skill1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_name_assault_skill2</t>
+  </si>
+  <si>
+    <t>text_card_name_assault_skill3</t>
+  </si>
+  <si>
+    <t>text_card_name_assault_skill4</t>
+  </si>
+  <si>
+    <t>text_card_name_assault_skill5</t>
+  </si>
+  <si>
+    <t>text_card_desc_assault_skill1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>text_card_desc_assault_skill2</t>
+  </si>
+  <si>
+    <t>text_card_desc_assault_skill3</t>
+  </si>
+  <si>
+    <t>text_card_desc_assault_skill4</t>
+  </si>
+  <si>
+    <t>text_card_desc_assault_skill5</t>
   </si>
 </sst>
 </file>
@@ -619,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -633,8 +633,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -936,7 +934,7 @@
       <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G2" s="2">
@@ -958,7 +956,7 @@
         <v>19</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="N2" s="2">
         <v>5</v>
@@ -984,7 +982,7 @@
       <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G3" s="2">
@@ -1032,7 +1030,7 @@
       <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="2">
@@ -1080,7 +1078,7 @@
       <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G5" s="2">
@@ -1132,7 +1130,7 @@
       <c r="E6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="2">
@@ -1180,7 +1178,7 @@
       <c r="E7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G7" s="3">
@@ -1232,7 +1230,7 @@
       <c r="E8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="2">
@@ -1276,7 +1274,7 @@
       <c r="E9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="1" t="s">
         <v>44</v>
       </c>
       <c r="G9" s="2">
@@ -1320,7 +1318,7 @@
       <c r="E10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="1" t="s">
         <v>48</v>
       </c>
       <c r="G10" s="2">
@@ -1364,7 +1362,7 @@
       <c r="E11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="1" t="s">
         <v>52</v>
       </c>
       <c r="G11" s="2">
@@ -1408,7 +1406,7 @@
       <c r="E12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="1" t="s">
         <v>57</v>
       </c>
       <c r="G12" s="2">
@@ -1456,7 +1454,7 @@
       <c r="E13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="1" t="s">
         <v>63</v>
       </c>
       <c r="G13" s="2">
@@ -1504,7 +1502,7 @@
       <c r="E14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="3" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="2">
@@ -1552,7 +1550,7 @@
       <c r="E15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="1" t="s">
         <v>73</v>
       </c>
       <c r="G15" s="2">
@@ -1600,7 +1598,7 @@
       <c r="E16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="3" t="s">
         <v>63</v>
       </c>
       <c r="G16" s="2">
@@ -1640,7 +1638,7 @@
         <v>77</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>61</v>
@@ -1648,7 +1646,7 @@
       <c r="E17" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="3" t="s">
         <v>79</v>
       </c>
       <c r="G17" s="3">
@@ -1681,19 +1679,19 @@
         <v>10005</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>117</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
@@ -1711,10 +1709,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="N18" s="3">
         <v>1</v>
@@ -1725,19 +1723,19 @@
         <v>10006</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>138</v>
+      <c r="F19" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
@@ -1755,10 +1753,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="N19" s="3">
         <v>1</v>
@@ -1769,19 +1767,19 @@
         <v>10007</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>139</v>
+      <c r="F20" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="G20" s="3">
         <v>1</v>
@@ -1799,10 +1797,10 @@
         <v>0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>1</v>
@@ -1813,19 +1811,19 @@
         <v>10008</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>140</v>
+      <c r="F21" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
@@ -1843,10 +1841,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="N21" s="3">
         <v>1</v>
@@ -1857,19 +1855,19 @@
         <v>20101</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>141</v>
+        <v>113</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -1887,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="N22" s="2">
         <v>1</v>
@@ -1901,16 +1899,16 @@
         <v>82</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>142</v>
+        <v>114</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="G23" s="2">
         <v>1</v>
@@ -1928,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="N23" s="2">
         <v>1</v>
@@ -1942,16 +1940,16 @@
         <v>83</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>143</v>
+        <v>115</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>133</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -1969,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="N24" s="2">
         <v>1</v>
@@ -1983,16 +1981,16 @@
         <v>84</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>144</v>
+        <v>116</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -2010,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="N25" s="2">
         <v>1</v>
@@ -2024,16 +2022,16 @@
         <v>85</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>145</v>
+        <v>117</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>135</v>
       </c>
       <c r="G26" s="2">
         <v>1</v>
@@ -2051,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="N26" s="2">
         <v>1</v>
@@ -2062,19 +2060,19 @@
         <v>20201</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>86</v>
+        <v>152</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -2103,19 +2101,19 @@
         <v>20202</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -2144,19 +2142,19 @@
         <v>20203</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>88</v>
+        <v>154</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -2185,19 +2183,19 @@
         <v>20204</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -2226,19 +2224,19 @@
         <v>20205</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>90</v>
+        <v>156</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -2267,19 +2265,19 @@
         <v>20301</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="G32" s="2">
         <v>1</v>
@@ -2297,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -2308,19 +2306,19 @@
         <v>20302</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -2338,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -2349,19 +2347,19 @@
         <v>20303</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -2379,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -2390,19 +2388,19 @@
         <v>20304</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -2420,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -2431,19 +2429,19 @@
         <v>20305</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -2461,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N36">
         <v>1</v>
@@ -2472,19 +2470,19 @@
         <v>20401</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -2502,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="N37">
         <v>1</v>
@@ -2513,19 +2511,19 @@
         <v>20402</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="D38" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -2543,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -2554,19 +2552,19 @@
         <v>20403</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="E39" s="6" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -2584,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="N39">
         <v>1</v>
@@ -2595,19 +2593,19 @@
         <v>20404</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -2625,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -2636,19 +2634,19 @@
         <v>20405</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -2666,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="N41">
         <v>1</v>

--- a/Dev_GNC/TableData/CardDataTable.xlsx
+++ b/Dev_GNC/TableData/CardDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C5588D-2DB8-4E6C-90A4-370B8EEAA4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280A930B-E08B-42AE-B471-847F50E0BBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39180" yWindow="2460" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,6 @@
     <t>target</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
     <t>energyCost</t>
   </si>
   <si>
@@ -558,6 +552,14 @@
   </si>
   <si>
     <t>text_card_desc_assault_skill5</t>
+  </si>
+  <si>
+    <t>nameAlias</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>descAlias</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -876,46 +878,46 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="O1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
@@ -923,19 +925,19 @@
         <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -953,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N2" s="2">
         <v>5</v>
@@ -971,19 +973,19 @@
         <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -1001,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N3" s="2">
         <v>5</v>
@@ -1019,19 +1021,19 @@
         <v>103</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -1049,10 +1051,10 @@
         <v>0</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N4" s="2">
         <v>10</v>
@@ -1067,19 +1069,19 @@
         <v>104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -1097,16 +1099,16 @@
         <v>0</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N5" s="2">
         <v>5</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P5" s="2">
         <v>1</v>
@@ -1119,19 +1121,19 @@
         <v>105</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -1149,10 +1151,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N6" s="2">
         <v>10</v>
@@ -1167,19 +1169,19 @@
         <v>201</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -1197,16 +1199,16 @@
         <v>1</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N7" s="3">
         <v>10</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P7" s="3">
         <v>1</v>
@@ -1219,19 +1221,19 @@
         <v>202</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
@@ -1249,7 +1251,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="2"/>
@@ -1263,19 +1265,19 @@
         <v>203</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
@@ -1293,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="2"/>
@@ -1307,19 +1309,19 @@
         <v>204</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
@@ -1337,7 +1339,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="2"/>
@@ -1351,19 +1353,19 @@
         <v>205</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
@@ -1381,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="2"/>
@@ -1395,19 +1397,19 @@
         <v>206</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
@@ -1425,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N12" s="2">
         <v>5</v>
@@ -1443,19 +1445,19 @@
         <v>207</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
@@ -1473,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N13" s="2">
         <v>5</v>
@@ -1491,19 +1493,19 @@
         <v>10001</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -1521,10 +1523,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N14" s="2">
         <v>2</v>
@@ -1539,19 +1541,19 @@
         <v>10002</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -1569,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N15" s="2">
         <v>5</v>
@@ -1587,19 +1589,19 @@
         <v>10003</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -1617,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N16" s="2">
         <v>5</v>
@@ -1635,19 +1637,19 @@
         <v>10004</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="G17" s="3">
         <v>1</v>
@@ -1665,10 +1667,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N17" s="3">
         <v>2</v>
@@ -1679,19 +1681,19 @@
         <v>10005</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
@@ -1709,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N18" s="3">
         <v>1</v>
@@ -1723,19 +1725,19 @@
         <v>10006</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="F19" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
@@ -1753,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N19" s="3">
         <v>1</v>
@@ -1767,19 +1769,19 @@
         <v>10007</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G20" s="3">
         <v>1</v>
@@ -1797,10 +1799,10 @@
         <v>0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N20" s="3">
         <v>1</v>
@@ -1811,19 +1813,19 @@
         <v>10008</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
@@ -1841,10 +1843,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N21" s="3">
         <v>1</v>
@@ -1855,37 +1857,37 @@
         <v>20101</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
-        <v>0</v>
-      </c>
-      <c r="K22" s="2">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="N22" s="2">
         <v>1</v>
@@ -1896,37 +1898,37 @@
         <v>20102</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G23" s="2">
-        <v>1</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2">
-        <v>0</v>
-      </c>
-      <c r="K23" s="2">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="N23" s="2">
         <v>1</v>
@@ -1937,37 +1939,37 @@
         <v>20103</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1</v>
-      </c>
-      <c r="H24" s="2">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2">
-        <v>0</v>
-      </c>
-      <c r="K24" s="2">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="N24" s="2">
         <v>1</v>
@@ -1978,37 +1980,37 @@
         <v>20104</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G25" s="2">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
-        <v>0</v>
-      </c>
-      <c r="K25" s="2">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="N25" s="2">
         <v>1</v>
@@ -2019,37 +2021,37 @@
         <v>20105</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2">
-        <v>0</v>
-      </c>
-      <c r="K26" s="2">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="N26" s="2">
         <v>1</v>
@@ -2060,19 +2062,19 @@
         <v>20201</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -2090,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N27" s="2">
         <v>5</v>
@@ -2101,19 +2103,19 @@
         <v>20202</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G28" s="2">
         <v>1</v>
@@ -2131,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N28" s="2">
         <v>5</v>
@@ -2142,19 +2144,19 @@
         <v>20203</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
@@ -2172,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N29" s="2">
         <v>5</v>
@@ -2183,19 +2185,19 @@
         <v>20204</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -2213,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N30" s="2">
         <v>5</v>
@@ -2224,19 +2226,19 @@
         <v>20205</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G31" s="2">
         <v>1</v>
@@ -2254,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N31" s="2">
         <v>5</v>
@@ -2265,37 +2267,37 @@
         <v>20301</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D32" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2">
+        <v>0</v>
+      </c>
+      <c r="M32" t="s">
         <v>98</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G32" s="2">
-        <v>1</v>
-      </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2">
-        <v>0</v>
-      </c>
-      <c r="M32" t="s">
-        <v>100</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -2306,37 +2308,37 @@
         <v>20302</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D33" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G33" s="2">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0</v>
+      </c>
+      <c r="M33" t="s">
         <v>98</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G33" s="2">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2">
-        <v>0</v>
-      </c>
-      <c r="I33" s="2">
-        <v>0</v>
-      </c>
-      <c r="J33" s="2">
-        <v>0</v>
-      </c>
-      <c r="K33" s="2">
-        <v>0</v>
-      </c>
-      <c r="M33" t="s">
-        <v>100</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -2347,37 +2349,37 @@
         <v>20303</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D34" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="2">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2">
+        <v>0</v>
+      </c>
+      <c r="M34" t="s">
         <v>98</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="G34" s="2">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2">
-        <v>0</v>
-      </c>
-      <c r="I34" s="2">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2">
-        <v>0</v>
-      </c>
-      <c r="M34" t="s">
-        <v>100</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -2388,37 +2390,37 @@
         <v>20304</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D35" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2">
+        <v>0</v>
+      </c>
+      <c r="M35" t="s">
         <v>98</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="G35" s="2">
-        <v>1</v>
-      </c>
-      <c r="H35" s="2">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2">
-        <v>0</v>
-      </c>
-      <c r="J35" s="2">
-        <v>0</v>
-      </c>
-      <c r="K35" s="2">
-        <v>0</v>
-      </c>
-      <c r="M35" t="s">
-        <v>100</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -2429,37 +2431,37 @@
         <v>20305</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D36" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2">
+        <v>0</v>
+      </c>
+      <c r="M36" t="s">
         <v>98</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1</v>
-      </c>
-      <c r="H36" s="2">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2">
-        <v>0</v>
-      </c>
-      <c r="M36" t="s">
-        <v>100</v>
       </c>
       <c r="N36">
         <v>1</v>
@@ -2470,19 +2472,19 @@
         <v>20401</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -2500,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N37">
         <v>1</v>
@@ -2511,19 +2513,19 @@
         <v>20402</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -2541,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -2552,19 +2554,19 @@
         <v>20403</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -2582,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N39">
         <v>1</v>
@@ -2593,19 +2595,19 @@
         <v>20404</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
@@ -2623,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -2634,19 +2636,19 @@
         <v>20405</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="D41" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G41" s="2">
         <v>1</v>
@@ -2664,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N41">
         <v>1</v>
